--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487150_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487150_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5894</v>
+        <v>2.9899</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8255</v>
+        <v>2.7442</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2361</v>
+        <v>0.2458</v>
       </c>
       <c r="G2" t="n">
         <v>1.3655</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7291</v>
+        <v>-1.3286</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8196</v>
+        <v>-0.9009</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9095</v>
+        <v>-0.4277</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3281</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2867</v>
+        <v>2.3383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5394</v>
+        <v>0.8587</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7473</v>
+        <v>1.4796</v>
       </c>
       <c r="G3" t="n">
         <v>1.8065</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1567</v>
+        <v>-1.1052</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2942</v>
+        <v>-0.9749</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1374</v>
+        <v>-0.1303</v>
       </c>
       <c r="V3" t="n">
         <v>0.2859</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>L. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0741</v>
+        <v>1.5638</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7243000000000001</v>
+        <v>-0.357</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3498</v>
+        <v>1.9207</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0546</v>
+        <v>-0.0123</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9221</v>
+        <v>-0.4699</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9768</v>
+        <v>0.4577</v>
       </c>
       <c r="J4" t="n">
-        <v>0.946</v>
+        <v>0.1663</v>
       </c>
       <c r="K4" t="n">
-        <v>1.63</v>
+        <v>-0.4763</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0006</v>
+        <v>-0.1786</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7079</v>
+        <v>0.0064</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2928</v>
+        <v>-0.185</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5441</v>
+        <v>2.7021</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5091</v>
+        <v>3.6672</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2988</v>
+        <v>-1.4542</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4574</v>
+        <v>-1.0721</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1587</v>
+        <v>-0.3821</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2859</v>
+        <v>0.3281</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GOMEZ FERNANDEZ</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0443</v>
+        <v>1.3255</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8764999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9207</v>
+        <v>1.2427</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0123</v>
+        <v>-0.0546</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4699</v>
+        <v>0.9221</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4577</v>
+        <v>-0.9768</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1663</v>
+        <v>0.946</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4763</v>
+        <v>1.63</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6425999999999999</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1786</v>
+        <v>-1.0006</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0064</v>
+        <v>-0.7079</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.185</v>
+        <v>-0.2928</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7021</v>
+        <v>1.5441</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6672</v>
+        <v>2.5091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9737</v>
+        <v>-0.4498</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.5916</v>
+        <v>-0.1841</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3821</v>
+        <v>-0.2657</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3518</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3272</v>
+        <v>-0.2271</v>
       </c>
       <c r="F6" t="n">
-        <v>0.679</v>
+        <v>0.7325</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5009</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8844</v>
+        <v>-0.7307</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8328</v>
+        <v>-0.7327</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0516</v>
+        <v>0.002</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2439</v>
+        <v>0.3371</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0245</v>
+        <v>0.2248</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2194</v>
+        <v>0.1123</v>
       </c>
       <c r="G7" t="n">
         <v>0.3371</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0925</v>
+        <v>0.1857</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.119</v>
+        <v>0.0813</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2115</v>
+        <v>0.1044</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5717</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9391</v>
+        <v>-1.5395</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.2744</v>
+        <v>-3.7142</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3353</v>
+        <v>2.1747</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5459</v>
@@ -1078,13 +1078,13 @@
         <v>3.6672</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5163</v>
+        <v>-1.1167</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.6511</v>
+        <v>-1.0909</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1348</v>
+        <v>-0.0258</v>
       </c>
       <c r="V8" t="n">
         <v>-0.614</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.165</v>
+        <v>-2.4397</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0839</v>
+        <v>-3.4657</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9189000000000001</v>
+        <v>1.026</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6201</v>
@@ -1156,13 +1156,13 @@
         <v>3.6672</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2215</v>
+        <v>-1.4961</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.9356</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6676</v>
+        <v>-0.5606</v>
       </c>
       <c r="V9" t="n">
         <v>1.7997</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.4861</v>
+        <v>5.080899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4483</v>
+        <v>-3.8535</v>
       </c>
       <c r="F10" t="n">
         <v>8.9343</v>
@@ -1234,10 +1234,10 @@
         <v>21.231</v>
       </c>
       <c r="S10" t="n">
-        <v>-8.090400000000001</v>
+        <v>-7.4956</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.4048</v>
+        <v>-5.8099</v>
       </c>
       <c r="U10" t="n">
         <v>-1.6858</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.5876</v>
+        <v>6.4221</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0272</v>
+        <v>4.7282</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5604</v>
+        <v>1.6939</v>
       </c>
       <c r="G11" t="n">
         <v>5.9253</v>
@@ -1312,13 +1312,13 @@
         <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0013</v>
+        <v>0.8358</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5803</v>
+        <v>0.1207</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5816</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>2.1701</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.667</v>
+        <v>3.6111</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6475</v>
+        <v>3.0467</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0195</v>
+        <v>0.5644</v>
       </c>
       <c r="G12" t="n">
         <v>4.6677</v>
@@ -1390,13 +1390,13 @@
         <v>2.1231</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3347</v>
+        <v>2.2788</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3762</v>
+        <v>0.7754</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9584</v>
+        <v>1.5034</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5983</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5362</v>
+        <v>2.1154</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0656</v>
+        <v>0.1629</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4707</v>
+        <v>1.9525</v>
       </c>
       <c r="G13" t="n">
         <v>1.428</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5099</v>
+        <v>2.0891</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3063</v>
+        <v>1.4036</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2036</v>
+        <v>0.6854</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2436</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9661</v>
+        <v>-0.4657</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7506</v>
+        <v>-2.2499</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7846</v>
+        <v>1.7843</v>
       </c>
       <c r="G14" t="n">
         <v>-2.3731</v>
@@ -1546,13 +1546,13 @@
         <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7581</v>
+        <v>1.2585</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3291</v>
+        <v>0.1716</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0873</v>
+        <v>1.087</v>
       </c>
       <c r="V14" t="n">
         <v>1.228</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.5662</v>
+        <v>-1.5254</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.9313</v>
+        <v>-1.1435</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3652</v>
+        <v>-0.3819</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7492</v>
+        <v>0.0536</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3601</v>
+        <v>0.4606</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3891</v>
+        <v>-0.407</v>
       </c>
       <c r="J15" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0207</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0243</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7942</v>
+        <v>0.0536</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3808</v>
+        <v>0.4606</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4134</v>
+        <v>-0.407</v>
       </c>
       <c r="P15" t="n">
         <v>-0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1481</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0462</v>
+        <v>-0.1785</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1943</v>
+        <v>0.1785</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.766</v>
+        <v>-1.7276</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1435</v>
+        <v>-3.0662</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6225000000000001</v>
+        <v>1.3386</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0536</v>
+        <v>-1.2891</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4606</v>
+        <v>0.3603</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.407</v>
+        <v>-1.6494</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.8622</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.035</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.8971</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0536</v>
+        <v>-0.4269</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4606</v>
+        <v>-0.6747</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.407</v>
+        <v>0.2478</v>
       </c>
       <c r="P16" t="n">
         <v>-0.965</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2406</v>
+        <v>0.8124</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1785</v>
+        <v>-0.2739</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0621</v>
+        <v>1.0863</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GORDILLO BELTRAN</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.206</v>
+        <v>-1.8332</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0889</v>
+        <v>-2.3319</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1171</v>
+        <v>0.4987</v>
       </c>
       <c r="G17" t="n">
-        <v>0.067</v>
+        <v>-0.7492</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0487</v>
+        <v>-0.3601</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1157</v>
+        <v>-0.3891</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9411</v>
+        <v>0.045</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6726</v>
+        <v>0.0207</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2685</v>
+        <v>0.0243</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8741</v>
+        <v>-0.7942</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.3808</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1528</v>
+        <v>-0.4134</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7371</v>
+        <v>-0.965</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6921</v>
+        <v>-0.119</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2512</v>
+        <v>-0.4468</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4409</v>
+        <v>0.3278</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>A. GORDILLO BELTRAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7892</v>
+        <v>-1.9254</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.9675</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1783</v>
+        <v>-1.0368</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2891</v>
+        <v>0.067</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3603</v>
+        <v>-0.0487</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6494</v>
+        <v>0.1157</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8622</v>
+        <v>0.9411</v>
       </c>
       <c r="K18" t="n">
-        <v>1.035</v>
+        <v>0.6726</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.8971</v>
+        <v>0.2685</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4269</v>
+        <v>-0.8741</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6747</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2478</v>
+        <v>-0.1528</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.965</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R18" t="n">
-        <v>0.965</v>
+        <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2492</v>
+        <v>0.9726</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1752</v>
+        <v>0.4515</v>
       </c>
       <c r="U18" t="n">
-        <v>0.926</v>
+        <v>0.5212</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2859</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5686</v>
+        <v>-3.4893</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.202</v>
+        <v>-2.8014</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3667</v>
+        <v>-0.6879</v>
       </c>
       <c r="G19" t="n">
         <v>-3.8158</v>
@@ -1936,13 +1936,13 @@
         <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0542</v>
+        <v>0.1335</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6544</v>
+        <v>-0.2538</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7086</v>
+        <v>0.3873</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.4147</v>
+        <v>-5.0003</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5908</v>
+        <v>-4.3905</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8239</v>
+        <v>-0.6098</v>
       </c>
       <c r="G20" t="n">
         <v>-4.6897</v>
@@ -2014,13 +2014,13 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>0.082</v>
+        <v>0.4964</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2842</v>
+        <v>-0.0839</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3662</v>
+        <v>0.5803</v>
       </c>
       <c r="V20" t="n">
         <v>-0.614</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.486000000000001</v>
+        <v>-3.8183</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.9343</v>
+        <v>-8.934199999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>4.4485</v>
+        <v>5.116</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7753000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>10.6154</v>
       </c>
       <c r="S21" t="n">
-        <v>8.0906</v>
+        <v>8.758099999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6858</v>
+        <v>1.6859</v>
       </c>
       <c r="U21" t="n">
-        <v>6.4048</v>
+        <v>7.0724</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1857</v>
